--- a/artfynd/A 6847-2026 artfynd.xlsx
+++ b/artfynd/A 6847-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132013687</v>
       </c>
       <c r="B2" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132013659</v>
+        <v>132013651</v>
       </c>
       <c r="B3" t="n">
         <v>8455</v>
@@ -806,7 +806,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439359</v>
+        <v>439293</v>
       </c>
       <c r="R3" t="n">
-        <v>6781091</v>
+        <v>6781229</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132013656</v>
+        <v>132013659</v>
       </c>
       <c r="B4" t="n">
         <v>8455</v>
@@ -913,7 +913,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439249</v>
+        <v>439359</v>
       </c>
       <c r="R4" t="n">
-        <v>6781191</v>
+        <v>6781091</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132013651</v>
+        <v>132013656</v>
       </c>
       <c r="B5" t="n">
         <v>8455</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439293</v>
+        <v>439249</v>
       </c>
       <c r="R5" t="n">
-        <v>6781229</v>
+        <v>6781191</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,54 +1093,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132013648</v>
+        <v>132013688</v>
       </c>
       <c r="B6" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439237</v>
+        <v>439363</v>
       </c>
       <c r="R6" t="n">
-        <v>6781292</v>
+        <v>6781030</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1172,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1200,54 +1190,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132013650</v>
+        <v>132013682</v>
       </c>
       <c r="B7" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439293</v>
+        <v>439297</v>
       </c>
       <c r="R7" t="n">
-        <v>6781237</v>
+        <v>6781183</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,7 +1269,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1307,54 +1287,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132013653</v>
+        <v>132013619</v>
       </c>
       <c r="B8" t="n">
-        <v>8455</v>
+        <v>79936</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439292</v>
+        <v>439376</v>
       </c>
       <c r="R8" t="n">
-        <v>6781219</v>
+        <v>6781031</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,7 +1366,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1414,45 +1384,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132013619</v>
+        <v>132013653</v>
       </c>
       <c r="B9" t="n">
-        <v>79934</v>
+        <v>8455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439376</v>
+        <v>439292</v>
       </c>
       <c r="R9" t="n">
-        <v>6781031</v>
+        <v>6781219</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,6 +1472,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1511,45 +1491,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132013688</v>
+        <v>132013648</v>
       </c>
       <c r="B10" t="n">
-        <v>79315</v>
+        <v>8455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>439363</v>
+        <v>439237</v>
       </c>
       <c r="R10" t="n">
-        <v>6781030</v>
+        <v>6781292</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,6 +1579,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1608,45 +1598,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132013682</v>
+        <v>132013650</v>
       </c>
       <c r="B11" t="n">
-        <v>79315</v>
+        <v>8455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439297</v>
+        <v>439293</v>
       </c>
       <c r="R11" t="n">
-        <v>6781183</v>
+        <v>6781237</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1687,6 +1686,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132013627</v>
+        <v>132013612</v>
       </c>
       <c r="B12" t="n">
-        <v>57945</v>
+        <v>79936</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,42 +1716,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439286</v>
+        <v>439240</v>
       </c>
       <c r="R12" t="n">
-        <v>6781084</v>
+        <v>6781353</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132013612</v>
+        <v>132013685</v>
       </c>
       <c r="B13" t="n">
-        <v>79934</v>
+        <v>79317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1821,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1845,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439240</v>
+        <v>439329</v>
       </c>
       <c r="R13" t="n">
-        <v>6781353</v>
+        <v>6781100</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132013685</v>
+        <v>132013627</v>
       </c>
       <c r="B14" t="n">
-        <v>79315</v>
+        <v>57945</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1918,34 +1910,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439329</v>
+        <v>439286</v>
       </c>
       <c r="R14" t="n">
-        <v>6781100</v>
+        <v>6781084</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2323,54 +2323,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132013654</v>
+        <v>132013684</v>
       </c>
       <c r="B18" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439289</v>
+        <v>439327</v>
       </c>
       <c r="R18" t="n">
-        <v>6781237</v>
+        <v>6781115</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2411,7 +2402,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2433,7 +2423,7 @@
         <v>132013676</v>
       </c>
       <c r="B19" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,45 +2517,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132013684</v>
+        <v>132013654</v>
       </c>
       <c r="B20" t="n">
-        <v>79315</v>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439327</v>
+        <v>439289</v>
       </c>
       <c r="R20" t="n">
-        <v>6781115</v>
+        <v>6781237</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2606,6 +2605,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2624,10 +2624,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132013680</v>
+        <v>132013640</v>
       </c>
       <c r="B21" t="n">
-        <v>79315</v>
+        <v>57945</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2635,34 +2635,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439265</v>
+        <v>439378</v>
       </c>
       <c r="R21" t="n">
-        <v>6781191</v>
+        <v>6781041</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2721,10 +2729,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132013675</v>
+        <v>132013680</v>
       </c>
       <c r="B22" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2756,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439249</v>
+        <v>439265</v>
       </c>
       <c r="R22" t="n">
-        <v>6781169</v>
+        <v>6781191</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132013640</v>
+        <v>132013675</v>
       </c>
       <c r="B23" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2829,42 +2837,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439378</v>
+        <v>439249</v>
       </c>
       <c r="R23" t="n">
-        <v>6781041</v>
+        <v>6781169</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3033,7 +3033,7 @@
         <v>132013686</v>
       </c>
       <c r="B25" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132013633</v>
+        <v>132013636</v>
       </c>
       <c r="B26" t="n">
         <v>57945</v>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439255</v>
+        <v>439308</v>
       </c>
       <c r="R26" t="n">
-        <v>6781203</v>
+        <v>6781186</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3241,7 +3241,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132013636</v>
+        <v>132013633</v>
       </c>
       <c r="B27" t="n">
         <v>57945</v>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439308</v>
+        <v>439255</v>
       </c>
       <c r="R27" t="n">
-        <v>6781186</v>
+        <v>6781203</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3456,7 +3456,7 @@
         <v>132013678</v>
       </c>
       <c r="B29" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132013638</v>
+        <v>132013643</v>
       </c>
       <c r="B31" t="n">
         <v>57945</v>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439341</v>
+        <v>439398</v>
       </c>
       <c r="R31" t="n">
-        <v>6781087</v>
+        <v>6781005</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3766,7 +3766,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132013643</v>
+        <v>132013638</v>
       </c>
       <c r="B32" t="n">
         <v>57945</v>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439398</v>
+        <v>439341</v>
       </c>
       <c r="R32" t="n">
-        <v>6781005</v>
+        <v>6781087</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4083,10 +4083,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132013631</v>
+        <v>132013679</v>
       </c>
       <c r="B35" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4094,42 +4094,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439275</v>
+        <v>439262</v>
       </c>
       <c r="R35" t="n">
-        <v>6781243</v>
+        <v>6781233</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4188,10 +4180,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132013679</v>
+        <v>132013681</v>
       </c>
       <c r="B36" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4223,10 +4215,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439262</v>
+        <v>439286</v>
       </c>
       <c r="R36" t="n">
-        <v>6781233</v>
+        <v>6781161</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4259,6 +4251,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4285,45 +4282,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132013681</v>
+        <v>132013623</v>
       </c>
       <c r="B37" t="n">
-        <v>79315</v>
+        <v>57136</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439286</v>
+        <v>439275</v>
       </c>
       <c r="R37" t="n">
-        <v>6781161</v>
+        <v>6781156</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4356,11 +4361,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4387,32 +4387,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132013623</v>
+        <v>132013631</v>
       </c>
       <c r="B38" t="n">
-        <v>57136</v>
+        <v>57945</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4433,7 +4433,7 @@
         <v>439275</v>
       </c>
       <c r="R38" t="n">
-        <v>6781156</v>
+        <v>6781243</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4492,10 +4492,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132013695</v>
+        <v>132013642</v>
       </c>
       <c r="B39" t="n">
-        <v>79315</v>
+        <v>57945</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4503,26 +4503,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4530,10 +4535,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439388</v>
+        <v>439403</v>
       </c>
       <c r="R39" t="n">
-        <v>6781029</v>
+        <v>6781014</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4574,7 +4579,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4593,10 +4597,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132013613</v>
+        <v>132013695</v>
       </c>
       <c r="B40" t="n">
-        <v>79934</v>
+        <v>79317</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4604,21 +4608,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4631,10 +4635,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439286</v>
+        <v>439388</v>
       </c>
       <c r="R40" t="n">
-        <v>6781160</v>
+        <v>6781029</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4694,10 +4698,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132013642</v>
+        <v>132013613</v>
       </c>
       <c r="B41" t="n">
-        <v>57945</v>
+        <v>79936</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4705,31 +4709,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4737,10 +4736,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439403</v>
+        <v>439286</v>
       </c>
       <c r="R41" t="n">
-        <v>6781014</v>
+        <v>6781160</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4781,6 +4780,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>132013617</v>
       </c>
       <c r="B43" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>132013674</v>
       </c>
       <c r="B44" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>132013618</v>
       </c>
       <c r="B45" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5201,10 +5201,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132013614</v>
+        <v>132013693</v>
       </c>
       <c r="B46" t="n">
-        <v>79934</v>
+        <v>79317</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5212,21 +5212,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439314</v>
+        <v>439233</v>
       </c>
       <c r="R46" t="n">
-        <v>6781147</v>
+        <v>6781356</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5298,45 +5298,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132013693</v>
+        <v>132013622</v>
       </c>
       <c r="B47" t="n">
-        <v>79315</v>
+        <v>57136</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439233</v>
+        <v>439391</v>
       </c>
       <c r="R47" t="n">
-        <v>6781356</v>
+        <v>6781007</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5395,10 +5403,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132013639</v>
+        <v>132013614</v>
       </c>
       <c r="B48" t="n">
-        <v>57945</v>
+        <v>79936</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5406,42 +5414,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439388</v>
+        <v>439314</v>
       </c>
       <c r="R48" t="n">
-        <v>6781058</v>
+        <v>6781147</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5500,32 +5500,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132013622</v>
+        <v>132013639</v>
       </c>
       <c r="B49" t="n">
-        <v>57136</v>
+        <v>57945</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5533,7 +5533,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5543,10 +5543,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439391</v>
+        <v>439388</v>
       </c>
       <c r="R49" t="n">
-        <v>6781007</v>
+        <v>6781058</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5715,7 +5715,7 @@
         <v>132013677</v>
       </c>
       <c r="B51" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>132013689</v>
       </c>
       <c r="B52" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132013641</v>
+        <v>132013615</v>
       </c>
       <c r="B54" t="n">
-        <v>57945</v>
+        <v>79936</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6022,31 +6022,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6054,10 +6049,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>439360</v>
+        <v>439324</v>
       </c>
       <c r="R54" t="n">
-        <v>6781051</v>
+        <v>6781110</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6098,6 +6093,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6116,10 +6112,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132013644</v>
+        <v>132013620</v>
       </c>
       <c r="B55" t="n">
-        <v>57945</v>
+        <v>79936</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6127,31 +6123,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6159,10 +6150,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>439349</v>
+        <v>439351</v>
       </c>
       <c r="R55" t="n">
-        <v>6781004</v>
+        <v>6780997</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6203,6 +6194,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6221,41 +6213,40 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132013649</v>
+        <v>132013641</v>
       </c>
       <c r="B56" t="n">
-        <v>8455</v>
+        <v>57945</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6265,10 +6256,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>439252</v>
+        <v>439360</v>
       </c>
       <c r="R56" t="n">
-        <v>6781254</v>
+        <v>6781051</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6309,7 +6300,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6328,10 +6318,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132013615</v>
+        <v>132013644</v>
       </c>
       <c r="B57" t="n">
-        <v>79934</v>
+        <v>57945</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6339,26 +6329,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6366,10 +6361,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>439324</v>
+        <v>439349</v>
       </c>
       <c r="R57" t="n">
-        <v>6781110</v>
+        <v>6781004</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6410,7 +6405,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6429,37 +6423,43 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132013620</v>
+        <v>132013649</v>
       </c>
       <c r="B58" t="n">
-        <v>79934</v>
+        <v>8455</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6467,10 +6467,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439351</v>
+        <v>439252</v>
       </c>
       <c r="R58" t="n">
-        <v>6780997</v>
+        <v>6781254</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 6847-2026 artfynd.xlsx
+++ b/artfynd/A 6847-2026 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132013687</v>
+        <v>132013651</v>
       </c>
       <c r="B2" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>439367</v>
+        <v>439293</v>
       </c>
       <c r="R2" t="n">
-        <v>6781024</v>
+        <v>6781229</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132013651</v>
+        <v>132013659</v>
       </c>
       <c r="B3" t="n">
         <v>8455</v>
@@ -806,7 +816,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -816,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439293</v>
+        <v>439359</v>
       </c>
       <c r="R3" t="n">
-        <v>6781229</v>
+        <v>6781091</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132013659</v>
+        <v>132013656</v>
       </c>
       <c r="B4" t="n">
         <v>8455</v>
@@ -913,7 +923,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -923,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439359</v>
+        <v>439249</v>
       </c>
       <c r="R4" t="n">
-        <v>6781091</v>
+        <v>6781191</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,54 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132013656</v>
+        <v>132013687</v>
       </c>
       <c r="B5" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439249</v>
+        <v>439367</v>
       </c>
       <c r="R5" t="n">
-        <v>6781191</v>
+        <v>6781024</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1075,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1093,45 +1093,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132013688</v>
+        <v>132013653</v>
       </c>
       <c r="B6" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439363</v>
+        <v>439292</v>
       </c>
       <c r="R6" t="n">
-        <v>6781030</v>
+        <v>6781219</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,6 +1181,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1190,45 +1200,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132013682</v>
+        <v>132013648</v>
       </c>
       <c r="B7" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439297</v>
+        <v>439237</v>
       </c>
       <c r="R7" t="n">
-        <v>6781183</v>
+        <v>6781292</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,6 +1288,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1287,45 +1307,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132013619</v>
+        <v>132013650</v>
       </c>
       <c r="B8" t="n">
-        <v>79936</v>
+        <v>8455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439376</v>
+        <v>439293</v>
       </c>
       <c r="R8" t="n">
-        <v>6781031</v>
+        <v>6781237</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,6 +1395,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1384,54 +1414,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132013653</v>
+        <v>132013688</v>
       </c>
       <c r="B9" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439292</v>
+        <v>439363</v>
       </c>
       <c r="R9" t="n">
-        <v>6781219</v>
+        <v>6781030</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,7 +1493,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1491,54 +1511,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132013648</v>
+        <v>132013682</v>
       </c>
       <c r="B10" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>439237</v>
+        <v>439297</v>
       </c>
       <c r="R10" t="n">
-        <v>6781292</v>
+        <v>6781183</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,7 +1590,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1598,54 +1608,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132013650</v>
+        <v>132013619</v>
       </c>
       <c r="B11" t="n">
-        <v>8455</v>
+        <v>79936</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439293</v>
+        <v>439376</v>
       </c>
       <c r="R11" t="n">
-        <v>6781237</v>
+        <v>6781031</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,7 +1687,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2624,10 +2624,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132013640</v>
+        <v>132013680</v>
       </c>
       <c r="B21" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2635,42 +2635,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439378</v>
+        <v>439265</v>
       </c>
       <c r="R21" t="n">
-        <v>6781041</v>
+        <v>6781191</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2729,7 +2721,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132013680</v>
+        <v>132013675</v>
       </c>
       <c r="B22" t="n">
         <v>79317</v>
@@ -2764,10 +2756,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439265</v>
+        <v>439249</v>
       </c>
       <c r="R22" t="n">
-        <v>6781191</v>
+        <v>6781169</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,10 +2818,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132013675</v>
+        <v>132013640</v>
       </c>
       <c r="B23" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,34 +2829,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439249</v>
+        <v>439378</v>
       </c>
       <c r="R23" t="n">
-        <v>6781169</v>
+        <v>6781041</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3030,37 +3030,43 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132013686</v>
+        <v>132013663</v>
       </c>
       <c r="B25" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3068,10 +3074,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439333</v>
+        <v>439379</v>
       </c>
       <c r="R25" t="n">
-        <v>6781057</v>
+        <v>6781012</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3104,11 +3110,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3136,10 +3137,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132013636</v>
+        <v>132013686</v>
       </c>
       <c r="B26" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,31 +3148,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3179,10 +3175,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439308</v>
+        <v>439333</v>
       </c>
       <c r="R26" t="n">
-        <v>6781186</v>
+        <v>6781057</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3217,12 +3213,18 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3241,7 +3243,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132013633</v>
+        <v>132013636</v>
       </c>
       <c r="B27" t="n">
         <v>57945</v>
@@ -3284,10 +3286,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439255</v>
+        <v>439308</v>
       </c>
       <c r="R27" t="n">
-        <v>6781203</v>
+        <v>6781186</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3346,41 +3348,40 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132013663</v>
+        <v>132013633</v>
       </c>
       <c r="B28" t="n">
-        <v>8455</v>
+        <v>57945</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3390,10 +3391,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439379</v>
+        <v>439255</v>
       </c>
       <c r="R28" t="n">
-        <v>6781012</v>
+        <v>6781203</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3434,7 +3435,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4282,32 +4282,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132013623</v>
+        <v>132013631</v>
       </c>
       <c r="B37" t="n">
-        <v>57136</v>
+        <v>57945</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4328,7 +4328,7 @@
         <v>439275</v>
       </c>
       <c r="R37" t="n">
-        <v>6781156</v>
+        <v>6781243</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4387,32 +4387,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132013631</v>
+        <v>132013623</v>
       </c>
       <c r="B38" t="n">
-        <v>57945</v>
+        <v>57136</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4433,7 +4433,7 @@
         <v>439275</v>
       </c>
       <c r="R38" t="n">
-        <v>6781243</v>
+        <v>6781156</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5201,45 +5201,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132013693</v>
+        <v>132013652</v>
       </c>
       <c r="B46" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439233</v>
+        <v>439297</v>
       </c>
       <c r="R46" t="n">
-        <v>6781356</v>
+        <v>6781233</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5280,6 +5289,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5298,53 +5308,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132013622</v>
+        <v>132013693</v>
       </c>
       <c r="B47" t="n">
-        <v>57136</v>
+        <v>79317</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439391</v>
+        <v>439233</v>
       </c>
       <c r="R47" t="n">
-        <v>6781007</v>
+        <v>6781356</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5605,10 +5607,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132013652</v>
+        <v>132013622</v>
       </c>
       <c r="B50" t="n">
-        <v>8455</v>
+        <v>57136</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5616,30 +5618,29 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -5649,10 +5650,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>439297</v>
+        <v>439391</v>
       </c>
       <c r="R50" t="n">
-        <v>6781233</v>
+        <v>6781007</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5693,7 +5694,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6847-2026 artfynd.xlsx
+++ b/artfynd/A 6847-2026 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132013651</v>
+        <v>132013687</v>
       </c>
       <c r="B2" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>439293</v>
+        <v>439367</v>
       </c>
       <c r="R2" t="n">
-        <v>6781229</v>
+        <v>6781024</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132013659</v>
+        <v>132013651</v>
       </c>
       <c r="B3" t="n">
         <v>8455</v>
@@ -816,7 +806,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439359</v>
+        <v>439293</v>
       </c>
       <c r="R3" t="n">
-        <v>6781091</v>
+        <v>6781229</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132013656</v>
+        <v>132013659</v>
       </c>
       <c r="B4" t="n">
         <v>8455</v>
@@ -923,7 +913,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -933,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439249</v>
+        <v>439359</v>
       </c>
       <c r="R4" t="n">
-        <v>6781191</v>
+        <v>6781091</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,45 +986,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132013687</v>
+        <v>132013656</v>
       </c>
       <c r="B5" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439367</v>
+        <v>439249</v>
       </c>
       <c r="R5" t="n">
-        <v>6781024</v>
+        <v>6781191</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,6 +1074,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1093,54 +1093,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132013653</v>
+        <v>132013688</v>
       </c>
       <c r="B6" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439292</v>
+        <v>439363</v>
       </c>
       <c r="R6" t="n">
-        <v>6781219</v>
+        <v>6781030</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1172,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1200,54 +1190,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132013648</v>
+        <v>132013682</v>
       </c>
       <c r="B7" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439237</v>
+        <v>439297</v>
       </c>
       <c r="R7" t="n">
-        <v>6781292</v>
+        <v>6781183</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,7 +1269,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1307,54 +1287,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132013650</v>
+        <v>132013619</v>
       </c>
       <c r="B8" t="n">
-        <v>8455</v>
+        <v>79936</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439293</v>
+        <v>439376</v>
       </c>
       <c r="R8" t="n">
-        <v>6781237</v>
+        <v>6781031</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,7 +1366,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1414,45 +1384,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132013688</v>
+        <v>132013653</v>
       </c>
       <c r="B9" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439363</v>
+        <v>439292</v>
       </c>
       <c r="R9" t="n">
-        <v>6781030</v>
+        <v>6781219</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,6 +1472,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1511,45 +1491,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132013682</v>
+        <v>132013648</v>
       </c>
       <c r="B10" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>439297</v>
+        <v>439237</v>
       </c>
       <c r="R10" t="n">
-        <v>6781183</v>
+        <v>6781292</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,6 +1579,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1608,45 +1598,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132013619</v>
+        <v>132013650</v>
       </c>
       <c r="B11" t="n">
-        <v>79936</v>
+        <v>8455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439376</v>
+        <v>439293</v>
       </c>
       <c r="R11" t="n">
-        <v>6781031</v>
+        <v>6781237</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1687,6 +1686,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2323,7 +2323,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132013684</v>
+        <v>132013676</v>
       </c>
       <c r="B18" t="n">
         <v>79317</v>
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439327</v>
+        <v>439220</v>
       </c>
       <c r="R18" t="n">
-        <v>6781115</v>
+        <v>6781321</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2420,7 +2420,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132013676</v>
+        <v>132013684</v>
       </c>
       <c r="B19" t="n">
         <v>79317</v>
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439220</v>
+        <v>439327</v>
       </c>
       <c r="R19" t="n">
-        <v>6781321</v>
+        <v>6781115</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3030,43 +3030,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132013663</v>
+        <v>132013686</v>
       </c>
       <c r="B25" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3074,10 +3068,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439379</v>
+        <v>439333</v>
       </c>
       <c r="R25" t="n">
-        <v>6781012</v>
+        <v>6781057</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3110,6 +3104,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3137,10 +3136,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132013686</v>
+        <v>132013636</v>
       </c>
       <c r="B26" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3148,26 +3147,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3175,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439333</v>
+        <v>439308</v>
       </c>
       <c r="R26" t="n">
-        <v>6781057</v>
+        <v>6781186</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3213,18 +3217,12 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3243,7 +3241,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132013636</v>
+        <v>132013633</v>
       </c>
       <c r="B27" t="n">
         <v>57945</v>
@@ -3286,10 +3284,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439308</v>
+        <v>439255</v>
       </c>
       <c r="R27" t="n">
-        <v>6781186</v>
+        <v>6781203</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3348,40 +3346,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132013633</v>
+        <v>132013663</v>
       </c>
       <c r="B28" t="n">
-        <v>57945</v>
+        <v>8455</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3391,10 +3390,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439255</v>
+        <v>439379</v>
       </c>
       <c r="R28" t="n">
-        <v>6781203</v>
+        <v>6781012</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3435,6 +3434,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4906,10 +4906,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132013617</v>
+        <v>132013674</v>
       </c>
       <c r="B43" t="n">
-        <v>79936</v>
+        <v>79317</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4917,21 +4917,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>439388</v>
+        <v>439310</v>
       </c>
       <c r="R43" t="n">
-        <v>6781060</v>
+        <v>6781051</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5003,10 +5003,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132013674</v>
+        <v>132013617</v>
       </c>
       <c r="B44" t="n">
-        <v>79317</v>
+        <v>79936</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5014,21 +5014,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5038,10 +5038,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439310</v>
+        <v>439388</v>
       </c>
       <c r="R44" t="n">
-        <v>6781051</v>
+        <v>6781060</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6213,40 +6213,41 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132013641</v>
+        <v>132013649</v>
       </c>
       <c r="B56" t="n">
-        <v>57945</v>
+        <v>8455</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6256,10 +6257,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>439360</v>
+        <v>439252</v>
       </c>
       <c r="R56" t="n">
-        <v>6781051</v>
+        <v>6781254</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6300,6 +6301,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6318,7 +6320,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132013644</v>
+        <v>132013641</v>
       </c>
       <c r="B57" t="n">
         <v>57945</v>
@@ -6361,10 +6363,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>439349</v>
+        <v>439360</v>
       </c>
       <c r="R57" t="n">
-        <v>6781004</v>
+        <v>6781051</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6423,41 +6425,40 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132013649</v>
+        <v>132013644</v>
       </c>
       <c r="B58" t="n">
-        <v>8455</v>
+        <v>57945</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6467,10 +6468,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439252</v>
+        <v>439349</v>
       </c>
       <c r="R58" t="n">
-        <v>6781254</v>
+        <v>6781004</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6511,7 +6512,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6847-2026 artfynd.xlsx
+++ b/artfynd/A 6847-2026 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132013651</v>
+        <v>132013659</v>
       </c>
       <c r="B3" t="n">
         <v>8455</v>
@@ -806,7 +806,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439293</v>
+        <v>439359</v>
       </c>
       <c r="R3" t="n">
-        <v>6781229</v>
+        <v>6781091</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132013659</v>
+        <v>132013656</v>
       </c>
       <c r="B4" t="n">
         <v>8455</v>
@@ -913,7 +913,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439359</v>
+        <v>439249</v>
       </c>
       <c r="R4" t="n">
-        <v>6781091</v>
+        <v>6781191</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132013656</v>
+        <v>132013651</v>
       </c>
       <c r="B5" t="n">
         <v>8455</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439249</v>
+        <v>439293</v>
       </c>
       <c r="R5" t="n">
-        <v>6781191</v>
+        <v>6781229</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,45 +1093,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132013688</v>
+        <v>132013648</v>
       </c>
       <c r="B6" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439363</v>
+        <v>439237</v>
       </c>
       <c r="R6" t="n">
-        <v>6781030</v>
+        <v>6781292</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,6 +1181,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1190,45 +1200,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132013682</v>
+        <v>132013650</v>
       </c>
       <c r="B7" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439297</v>
+        <v>439293</v>
       </c>
       <c r="R7" t="n">
-        <v>6781183</v>
+        <v>6781237</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,6 +1288,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1287,45 +1307,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132013619</v>
+        <v>132013653</v>
       </c>
       <c r="B8" t="n">
-        <v>79936</v>
+        <v>8455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439376</v>
+        <v>439292</v>
       </c>
       <c r="R8" t="n">
-        <v>6781031</v>
+        <v>6781219</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,6 +1395,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1384,54 +1414,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132013653</v>
+        <v>132013688</v>
       </c>
       <c r="B9" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439292</v>
+        <v>439363</v>
       </c>
       <c r="R9" t="n">
-        <v>6781219</v>
+        <v>6781030</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,7 +1493,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1491,54 +1511,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132013648</v>
+        <v>132013682</v>
       </c>
       <c r="B10" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>439237</v>
+        <v>439297</v>
       </c>
       <c r="R10" t="n">
-        <v>6781292</v>
+        <v>6781183</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,7 +1590,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1598,54 +1608,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132013650</v>
+        <v>132013619</v>
       </c>
       <c r="B11" t="n">
-        <v>8455</v>
+        <v>79936</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439293</v>
+        <v>439376</v>
       </c>
       <c r="R11" t="n">
-        <v>6781237</v>
+        <v>6781031</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,7 +1687,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132013612</v>
+        <v>132013627</v>
       </c>
       <c r="B12" t="n">
-        <v>79936</v>
+        <v>57945</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,34 +1716,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439240</v>
+        <v>439286</v>
       </c>
       <c r="R12" t="n">
-        <v>6781353</v>
+        <v>6781084</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1907,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132013627</v>
+        <v>132013612</v>
       </c>
       <c r="B14" t="n">
-        <v>57945</v>
+        <v>79936</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1910,42 +1918,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439286</v>
+        <v>439240</v>
       </c>
       <c r="R14" t="n">
-        <v>6781084</v>
+        <v>6781353</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2323,7 +2323,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132013676</v>
+        <v>132013684</v>
       </c>
       <c r="B18" t="n">
         <v>79317</v>
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439220</v>
+        <v>439327</v>
       </c>
       <c r="R18" t="n">
-        <v>6781321</v>
+        <v>6781115</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2420,7 +2420,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132013684</v>
+        <v>132013676</v>
       </c>
       <c r="B19" t="n">
         <v>79317</v>
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439327</v>
+        <v>439220</v>
       </c>
       <c r="R19" t="n">
-        <v>6781115</v>
+        <v>6781321</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2624,45 +2624,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132013680</v>
+        <v>132013661</v>
       </c>
       <c r="B21" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439265</v>
+        <v>439403</v>
       </c>
       <c r="R21" t="n">
-        <v>6781191</v>
+        <v>6781018</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2703,6 +2712,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2818,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132013640</v>
+        <v>132013680</v>
       </c>
       <c r="B23" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2829,42 +2839,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439378</v>
+        <v>439265</v>
       </c>
       <c r="R23" t="n">
-        <v>6781041</v>
+        <v>6781191</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,41 +2925,40 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132013661</v>
+        <v>132013640</v>
       </c>
       <c r="B24" t="n">
-        <v>8455</v>
+        <v>57945</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2967,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439403</v>
+        <v>439378</v>
       </c>
       <c r="R24" t="n">
-        <v>6781018</v>
+        <v>6781041</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3011,7 +3012,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3136,40 +3136,41 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132013636</v>
+        <v>132013663</v>
       </c>
       <c r="B26" t="n">
-        <v>57945</v>
+        <v>8455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3179,10 +3180,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439308</v>
+        <v>439379</v>
       </c>
       <c r="R26" t="n">
-        <v>6781186</v>
+        <v>6781012</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3223,6 +3224,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3241,7 +3243,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132013633</v>
+        <v>132013636</v>
       </c>
       <c r="B27" t="n">
         <v>57945</v>
@@ -3284,10 +3286,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439255</v>
+        <v>439308</v>
       </c>
       <c r="R27" t="n">
-        <v>6781203</v>
+        <v>6781186</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3346,41 +3348,40 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132013663</v>
+        <v>132013633</v>
       </c>
       <c r="B28" t="n">
-        <v>8455</v>
+        <v>57945</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3390,10 +3391,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439379</v>
+        <v>439255</v>
       </c>
       <c r="R28" t="n">
-        <v>6781012</v>
+        <v>6781203</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3434,7 +3435,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3661,40 +3661,41 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132013643</v>
+        <v>132013657</v>
       </c>
       <c r="B31" t="n">
-        <v>57945</v>
+        <v>8455</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3704,10 +3705,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439398</v>
+        <v>439325</v>
       </c>
       <c r="R31" t="n">
-        <v>6781005</v>
+        <v>6781116</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3748,6 +3749,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3871,41 +3873,40 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132013657</v>
+        <v>132013643</v>
       </c>
       <c r="B33" t="n">
-        <v>8455</v>
+        <v>57945</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3915,10 +3916,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439325</v>
+        <v>439398</v>
       </c>
       <c r="R33" t="n">
-        <v>6781116</v>
+        <v>6781005</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3959,7 +3960,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4492,40 +4492,41 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132013642</v>
+        <v>132013660</v>
       </c>
       <c r="B39" t="n">
-        <v>57945</v>
+        <v>8455</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4535,10 +4536,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439403</v>
+        <v>439381</v>
       </c>
       <c r="R39" t="n">
-        <v>6781014</v>
+        <v>6781035</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4579,6 +4580,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4799,41 +4801,40 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132013660</v>
+        <v>132013642</v>
       </c>
       <c r="B42" t="n">
-        <v>8455</v>
+        <v>57945</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -4843,10 +4844,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439381</v>
+        <v>439403</v>
       </c>
       <c r="R42" t="n">
-        <v>6781035</v>
+        <v>6781014</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4887,7 +4888,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4906,10 +4906,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132013674</v>
+        <v>132013617</v>
       </c>
       <c r="B43" t="n">
-        <v>79317</v>
+        <v>79936</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4917,21 +4917,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>439310</v>
+        <v>439388</v>
       </c>
       <c r="R43" t="n">
-        <v>6781051</v>
+        <v>6781060</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5003,10 +5003,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132013617</v>
+        <v>132013674</v>
       </c>
       <c r="B44" t="n">
-        <v>79936</v>
+        <v>79317</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5014,21 +5014,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5038,10 +5038,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439388</v>
+        <v>439310</v>
       </c>
       <c r="R44" t="n">
-        <v>6781060</v>
+        <v>6781051</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5308,45 +5308,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132013693</v>
+        <v>132013622</v>
       </c>
       <c r="B47" t="n">
-        <v>79317</v>
+        <v>57136</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439233</v>
+        <v>439391</v>
       </c>
       <c r="R47" t="n">
-        <v>6781356</v>
+        <v>6781007</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5502,10 +5510,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132013639</v>
+        <v>132013693</v>
       </c>
       <c r="B49" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5513,42 +5521,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439388</v>
+        <v>439233</v>
       </c>
       <c r="R49" t="n">
-        <v>6781058</v>
+        <v>6781356</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5607,32 +5607,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132013622</v>
+        <v>132013639</v>
       </c>
       <c r="B50" t="n">
-        <v>57136</v>
+        <v>57945</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5640,7 +5640,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -5650,10 +5650,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>439391</v>
+        <v>439388</v>
       </c>
       <c r="R50" t="n">
-        <v>6781007</v>
+        <v>6781058</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6011,37 +6011,43 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132013615</v>
+        <v>132013649</v>
       </c>
       <c r="B54" t="n">
-        <v>79936</v>
+        <v>8455</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6049,10 +6055,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>439324</v>
+        <v>439252</v>
       </c>
       <c r="R54" t="n">
-        <v>6781110</v>
+        <v>6781254</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6112,10 +6118,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132013620</v>
+        <v>132013641</v>
       </c>
       <c r="B55" t="n">
-        <v>79936</v>
+        <v>57945</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6123,26 +6129,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6150,10 +6161,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>439351</v>
+        <v>439360</v>
       </c>
       <c r="R55" t="n">
-        <v>6780997</v>
+        <v>6781051</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6194,7 +6205,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6213,41 +6223,40 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132013649</v>
+        <v>132013644</v>
       </c>
       <c r="B56" t="n">
-        <v>8455</v>
+        <v>57945</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6257,10 +6266,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>439252</v>
+        <v>439349</v>
       </c>
       <c r="R56" t="n">
-        <v>6781254</v>
+        <v>6781004</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6301,7 +6310,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6320,10 +6328,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132013641</v>
+        <v>132013615</v>
       </c>
       <c r="B57" t="n">
-        <v>57945</v>
+        <v>79936</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6331,31 +6339,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6363,10 +6366,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>439360</v>
+        <v>439324</v>
       </c>
       <c r="R57" t="n">
-        <v>6781051</v>
+        <v>6781110</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6407,6 +6410,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6425,10 +6429,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132013644</v>
+        <v>132013620</v>
       </c>
       <c r="B58" t="n">
-        <v>57945</v>
+        <v>79936</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6436,31 +6440,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6468,10 +6467,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439349</v>
+        <v>439351</v>
       </c>
       <c r="R58" t="n">
-        <v>6781004</v>
+        <v>6780997</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6512,6 +6511,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6847-2026 artfynd.xlsx
+++ b/artfynd/A 6847-2026 artfynd.xlsx
@@ -2323,45 +2323,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132013684</v>
+        <v>132013654</v>
       </c>
       <c r="B18" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439327</v>
+        <v>439289</v>
       </c>
       <c r="R18" t="n">
-        <v>6781115</v>
+        <v>6781237</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2402,6 +2411,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2420,7 +2430,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132013676</v>
+        <v>132013684</v>
       </c>
       <c r="B19" t="n">
         <v>79317</v>
@@ -2455,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439220</v>
+        <v>439327</v>
       </c>
       <c r="R19" t="n">
-        <v>6781321</v>
+        <v>6781115</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2517,54 +2527,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132013654</v>
+        <v>132013676</v>
       </c>
       <c r="B20" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439289</v>
+        <v>439220</v>
       </c>
       <c r="R20" t="n">
-        <v>6781237</v>
+        <v>6781321</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,7 +2606,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2624,54 +2624,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132013661</v>
+        <v>132013675</v>
       </c>
       <c r="B21" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439403</v>
+        <v>439249</v>
       </c>
       <c r="R21" t="n">
-        <v>6781018</v>
+        <v>6781169</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2712,7 +2703,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2731,10 +2721,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132013675</v>
+        <v>132013640</v>
       </c>
       <c r="B22" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2742,34 +2732,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439249</v>
+        <v>439378</v>
       </c>
       <c r="R22" t="n">
-        <v>6781169</v>
+        <v>6781041</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2828,45 +2826,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132013680</v>
+        <v>132013661</v>
       </c>
       <c r="B23" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439265</v>
+        <v>439403</v>
       </c>
       <c r="R23" t="n">
-        <v>6781191</v>
+        <v>6781018</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2907,6 +2914,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2925,10 +2933,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132013640</v>
+        <v>132013680</v>
       </c>
       <c r="B24" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2936,42 +2944,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439378</v>
+        <v>439265</v>
       </c>
       <c r="R24" t="n">
-        <v>6781041</v>
+        <v>6781191</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -5201,10 +5201,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132013652</v>
+        <v>132013622</v>
       </c>
       <c r="B46" t="n">
-        <v>8455</v>
+        <v>57136</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5212,30 +5212,29 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5245,10 +5244,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439297</v>
+        <v>439391</v>
       </c>
       <c r="R46" t="n">
-        <v>6781233</v>
+        <v>6781007</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5289,7 +5288,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5308,53 +5306,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132013622</v>
+        <v>132013614</v>
       </c>
       <c r="B47" t="n">
-        <v>57136</v>
+        <v>79936</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439391</v>
+        <v>439314</v>
       </c>
       <c r="R47" t="n">
-        <v>6781007</v>
+        <v>6781147</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5413,10 +5403,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132013614</v>
+        <v>132013693</v>
       </c>
       <c r="B48" t="n">
-        <v>79936</v>
+        <v>79317</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5424,21 +5414,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5448,10 +5438,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439314</v>
+        <v>439233</v>
       </c>
       <c r="R48" t="n">
-        <v>6781147</v>
+        <v>6781356</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5510,10 +5500,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132013693</v>
+        <v>132013639</v>
       </c>
       <c r="B49" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5521,34 +5511,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439233</v>
+        <v>439388</v>
       </c>
       <c r="R49" t="n">
-        <v>6781356</v>
+        <v>6781058</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5607,40 +5605,41 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132013639</v>
+        <v>132013652</v>
       </c>
       <c r="B50" t="n">
-        <v>57945</v>
+        <v>8455</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -5650,10 +5649,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>439388</v>
+        <v>439297</v>
       </c>
       <c r="R50" t="n">
-        <v>6781058</v>
+        <v>6781233</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5694,6 +5693,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6847-2026 artfynd.xlsx
+++ b/artfynd/A 6847-2026 artfynd.xlsx
@@ -2323,54 +2323,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132013654</v>
+        <v>132013684</v>
       </c>
       <c r="B18" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439289</v>
+        <v>439327</v>
       </c>
       <c r="R18" t="n">
-        <v>6781237</v>
+        <v>6781115</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2411,7 +2402,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2430,7 +2420,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132013684</v>
+        <v>132013676</v>
       </c>
       <c r="B19" t="n">
         <v>79317</v>
@@ -2465,10 +2455,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439327</v>
+        <v>439220</v>
       </c>
       <c r="R19" t="n">
-        <v>6781115</v>
+        <v>6781321</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2527,45 +2517,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132013676</v>
+        <v>132013654</v>
       </c>
       <c r="B20" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439220</v>
+        <v>439289</v>
       </c>
       <c r="R20" t="n">
-        <v>6781321</v>
+        <v>6781237</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2606,6 +2605,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2624,45 +2624,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132013675</v>
+        <v>132013661</v>
       </c>
       <c r="B21" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439249</v>
+        <v>439403</v>
       </c>
       <c r="R21" t="n">
-        <v>6781169</v>
+        <v>6781018</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2703,6 +2712,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2721,10 +2731,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132013640</v>
+        <v>132013675</v>
       </c>
       <c r="B22" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2732,42 +2742,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439378</v>
+        <v>439249</v>
       </c>
       <c r="R22" t="n">
-        <v>6781041</v>
+        <v>6781169</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,54 +2828,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132013661</v>
+        <v>132013680</v>
       </c>
       <c r="B23" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439403</v>
+        <v>439265</v>
       </c>
       <c r="R23" t="n">
-        <v>6781018</v>
+        <v>6781191</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2914,7 +2907,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2933,10 +2925,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132013680</v>
+        <v>132013640</v>
       </c>
       <c r="B24" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2944,34 +2936,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439265</v>
+        <v>439378</v>
       </c>
       <c r="R24" t="n">
-        <v>6781191</v>
+        <v>6781041</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -4083,45 +4083,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132013679</v>
+        <v>132013623</v>
       </c>
       <c r="B35" t="n">
-        <v>79317</v>
+        <v>57136</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439262</v>
+        <v>439275</v>
       </c>
       <c r="R35" t="n">
-        <v>6781233</v>
+        <v>6781156</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4180,7 +4188,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132013681</v>
+        <v>132013679</v>
       </c>
       <c r="B36" t="n">
         <v>79317</v>
@@ -4215,10 +4223,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439286</v>
+        <v>439262</v>
       </c>
       <c r="R36" t="n">
-        <v>6781161</v>
+        <v>6781233</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4251,11 +4259,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4282,10 +4285,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132013631</v>
+        <v>132013681</v>
       </c>
       <c r="B37" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4293,42 +4296,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439275</v>
+        <v>439286</v>
       </c>
       <c r="R37" t="n">
-        <v>6781243</v>
+        <v>6781161</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4361,6 +4356,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4387,32 +4387,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132013623</v>
+        <v>132013631</v>
       </c>
       <c r="B38" t="n">
-        <v>57136</v>
+        <v>57945</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4433,7 +4433,7 @@
         <v>439275</v>
       </c>
       <c r="R38" t="n">
-        <v>6781156</v>
+        <v>6781243</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5201,10 +5201,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132013622</v>
+        <v>132013652</v>
       </c>
       <c r="B46" t="n">
-        <v>57136</v>
+        <v>8455</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5212,29 +5212,30 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5244,10 +5245,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439391</v>
+        <v>439297</v>
       </c>
       <c r="R46" t="n">
-        <v>6781007</v>
+        <v>6781233</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5288,6 +5289,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5306,45 +5308,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132013614</v>
+        <v>132013622</v>
       </c>
       <c r="B47" t="n">
-        <v>79936</v>
+        <v>57136</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439314</v>
+        <v>439391</v>
       </c>
       <c r="R47" t="n">
-        <v>6781147</v>
+        <v>6781007</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5403,10 +5413,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132013693</v>
+        <v>132013614</v>
       </c>
       <c r="B48" t="n">
-        <v>79317</v>
+        <v>79936</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5414,21 +5424,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5438,10 +5448,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439233</v>
+        <v>439314</v>
       </c>
       <c r="R48" t="n">
-        <v>6781356</v>
+        <v>6781147</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5500,10 +5510,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132013639</v>
+        <v>132013693</v>
       </c>
       <c r="B49" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5511,42 +5521,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439388</v>
+        <v>439233</v>
       </c>
       <c r="R49" t="n">
-        <v>6781058</v>
+        <v>6781356</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5605,41 +5607,40 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132013652</v>
+        <v>132013639</v>
       </c>
       <c r="B50" t="n">
-        <v>8455</v>
+        <v>57945</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -5649,10 +5650,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>439297</v>
+        <v>439388</v>
       </c>
       <c r="R50" t="n">
-        <v>6781233</v>
+        <v>6781058</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5693,7 +5694,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6847-2026 artfynd.xlsx
+++ b/artfynd/A 6847-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132013687</v>
       </c>
       <c r="B2" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1093,54 +1093,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132013648</v>
+        <v>132013688</v>
       </c>
       <c r="B6" t="n">
-        <v>8455</v>
+        <v>79319</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439237</v>
+        <v>439363</v>
       </c>
       <c r="R6" t="n">
-        <v>6781292</v>
+        <v>6781030</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1172,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1200,54 +1190,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132013650</v>
+        <v>132013682</v>
       </c>
       <c r="B7" t="n">
-        <v>8455</v>
+        <v>79319</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439293</v>
+        <v>439297</v>
       </c>
       <c r="R7" t="n">
-        <v>6781237</v>
+        <v>6781183</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,7 +1269,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1307,54 +1287,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132013653</v>
+        <v>132013619</v>
       </c>
       <c r="B8" t="n">
-        <v>8455</v>
+        <v>79938</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439292</v>
+        <v>439376</v>
       </c>
       <c r="R8" t="n">
-        <v>6781219</v>
+        <v>6781031</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,7 +1366,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1414,45 +1384,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132013688</v>
+        <v>132013648</v>
       </c>
       <c r="B9" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439363</v>
+        <v>439237</v>
       </c>
       <c r="R9" t="n">
-        <v>6781030</v>
+        <v>6781292</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,6 +1472,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1511,45 +1491,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132013682</v>
+        <v>132013650</v>
       </c>
       <c r="B10" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>439297</v>
+        <v>439293</v>
       </c>
       <c r="R10" t="n">
-        <v>6781183</v>
+        <v>6781237</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,6 +1579,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1608,45 +1598,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132013619</v>
+        <v>132013653</v>
       </c>
       <c r="B11" t="n">
-        <v>79936</v>
+        <v>8455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439376</v>
+        <v>439292</v>
       </c>
       <c r="R11" t="n">
-        <v>6781031</v>
+        <v>6781219</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1687,6 +1686,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>132013627</v>
       </c>
       <c r="B12" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132013685</v>
+        <v>132013612</v>
       </c>
       <c r="B13" t="n">
-        <v>79317</v>
+        <v>79938</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1821,21 +1821,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439329</v>
+        <v>439240</v>
       </c>
       <c r="R13" t="n">
-        <v>6781100</v>
+        <v>6781353</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,45 +1907,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132013612</v>
+        <v>132013647</v>
       </c>
       <c r="B14" t="n">
-        <v>79936</v>
+        <v>8455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439240</v>
+        <v>439266</v>
       </c>
       <c r="R14" t="n">
-        <v>6781353</v>
+        <v>6781130</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,6 +1995,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2004,54 +2014,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132013662</v>
+        <v>132013685</v>
       </c>
       <c r="B15" t="n">
-        <v>8455</v>
+        <v>79319</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439398</v>
+        <v>439329</v>
       </c>
       <c r="R15" t="n">
-        <v>6781005</v>
+        <v>6781100</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2092,7 +2093,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132013647</v>
+        <v>132013662</v>
       </c>
       <c r="B16" t="n">
         <v>8455</v>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439266</v>
+        <v>439398</v>
       </c>
       <c r="R16" t="n">
-        <v>6781130</v>
+        <v>6781005</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2221,7 +2221,7 @@
         <v>132013637</v>
       </c>
       <c r="B17" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,10 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132013684</v>
+        <v>132013676</v>
       </c>
       <c r="B18" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439327</v>
+        <v>439220</v>
       </c>
       <c r="R18" t="n">
-        <v>6781115</v>
+        <v>6781321</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2420,10 +2420,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132013676</v>
+        <v>132013684</v>
       </c>
       <c r="B19" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439220</v>
+        <v>439327</v>
       </c>
       <c r="R19" t="n">
-        <v>6781321</v>
+        <v>6781115</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2624,54 +2624,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132013661</v>
+        <v>132013680</v>
       </c>
       <c r="B21" t="n">
-        <v>8455</v>
+        <v>79319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439403</v>
+        <v>439265</v>
       </c>
       <c r="R21" t="n">
-        <v>6781018</v>
+        <v>6781191</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2712,7 +2703,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2734,7 +2724,7 @@
         <v>132013675</v>
       </c>
       <c r="B22" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2828,10 +2818,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132013680</v>
+        <v>132013640</v>
       </c>
       <c r="B23" t="n">
-        <v>79317</v>
+        <v>57946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2839,34 +2829,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439265</v>
+        <v>439378</v>
       </c>
       <c r="R23" t="n">
-        <v>6781191</v>
+        <v>6781041</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,40 +2923,41 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132013640</v>
+        <v>132013661</v>
       </c>
       <c r="B24" t="n">
-        <v>57945</v>
+        <v>8455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2968,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439378</v>
+        <v>439403</v>
       </c>
       <c r="R24" t="n">
-        <v>6781041</v>
+        <v>6781018</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3012,6 +3011,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>132013686</v>
       </c>
       <c r="B25" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,41 +3136,40 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132013663</v>
+        <v>132013636</v>
       </c>
       <c r="B26" t="n">
-        <v>8455</v>
+        <v>57946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3180,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439379</v>
+        <v>439308</v>
       </c>
       <c r="R26" t="n">
-        <v>6781012</v>
+        <v>6781186</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3224,7 +3223,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3243,10 +3241,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132013636</v>
+        <v>132013633</v>
       </c>
       <c r="B27" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,10 +3284,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439308</v>
+        <v>439255</v>
       </c>
       <c r="R27" t="n">
-        <v>6781186</v>
+        <v>6781203</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3348,40 +3346,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132013633</v>
+        <v>132013663</v>
       </c>
       <c r="B28" t="n">
-        <v>57945</v>
+        <v>8455</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3391,10 +3390,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439255</v>
+        <v>439379</v>
       </c>
       <c r="R28" t="n">
-        <v>6781203</v>
+        <v>6781012</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3435,6 +3434,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3456,7 +3456,7 @@
         <v>132013678</v>
       </c>
       <c r="B29" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3661,41 +3661,40 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132013657</v>
+        <v>132013643</v>
       </c>
       <c r="B31" t="n">
-        <v>8455</v>
+        <v>57946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3705,10 +3704,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439325</v>
+        <v>439398</v>
       </c>
       <c r="R31" t="n">
-        <v>6781116</v>
+        <v>6781005</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3749,7 +3748,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3771,7 +3769,7 @@
         <v>132013638</v>
       </c>
       <c r="B32" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3873,40 +3871,41 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132013643</v>
+        <v>132013657</v>
       </c>
       <c r="B33" t="n">
-        <v>57945</v>
+        <v>8455</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3916,10 +3915,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439398</v>
+        <v>439325</v>
       </c>
       <c r="R33" t="n">
-        <v>6781005</v>
+        <v>6781116</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3960,6 +3959,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>132013628</v>
       </c>
       <c r="B34" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4083,53 +4083,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132013623</v>
+        <v>132013679</v>
       </c>
       <c r="B35" t="n">
-        <v>57136</v>
+        <v>79319</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439275</v>
+        <v>439262</v>
       </c>
       <c r="R35" t="n">
-        <v>6781156</v>
+        <v>6781233</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4188,10 +4180,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132013679</v>
+        <v>132013681</v>
       </c>
       <c r="B36" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4223,10 +4215,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439262</v>
+        <v>439286</v>
       </c>
       <c r="R36" t="n">
-        <v>6781233</v>
+        <v>6781161</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4259,6 +4251,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4285,10 +4282,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132013681</v>
+        <v>132013631</v>
       </c>
       <c r="B37" t="n">
-        <v>79317</v>
+        <v>57946</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4296,34 +4293,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439286</v>
+        <v>439275</v>
       </c>
       <c r="R37" t="n">
-        <v>6781161</v>
+        <v>6781243</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4356,11 +4361,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4387,32 +4387,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132013631</v>
+        <v>132013623</v>
       </c>
       <c r="B38" t="n">
-        <v>57945</v>
+        <v>57137</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4433,7 +4433,7 @@
         <v>439275</v>
       </c>
       <c r="R38" t="n">
-        <v>6781243</v>
+        <v>6781156</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4492,43 +4492,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132013660</v>
+        <v>132013695</v>
       </c>
       <c r="B39" t="n">
-        <v>8455</v>
+        <v>79319</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4536,10 +4530,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439381</v>
+        <v>439388</v>
       </c>
       <c r="R39" t="n">
-        <v>6781035</v>
+        <v>6781029</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4599,10 +4593,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132013695</v>
+        <v>132013642</v>
       </c>
       <c r="B40" t="n">
-        <v>79317</v>
+        <v>57946</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4610,26 +4604,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4637,10 +4636,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439388</v>
+        <v>439403</v>
       </c>
       <c r="R40" t="n">
-        <v>6781029</v>
+        <v>6781014</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4681,7 +4680,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4703,7 +4701,7 @@
         <v>132013613</v>
       </c>
       <c r="B41" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4801,40 +4799,41 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132013642</v>
+        <v>132013660</v>
       </c>
       <c r="B42" t="n">
-        <v>57945</v>
+        <v>8455</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -4844,10 +4843,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439403</v>
+        <v>439381</v>
       </c>
       <c r="R42" t="n">
-        <v>6781014</v>
+        <v>6781035</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4888,6 +4887,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4906,10 +4906,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132013617</v>
+        <v>132013674</v>
       </c>
       <c r="B43" t="n">
-        <v>79936</v>
+        <v>79319</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4917,21 +4917,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>439388</v>
+        <v>439310</v>
       </c>
       <c r="R43" t="n">
-        <v>6781060</v>
+        <v>6781051</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5003,10 +5003,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132013674</v>
+        <v>132013617</v>
       </c>
       <c r="B44" t="n">
-        <v>79317</v>
+        <v>79938</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5014,21 +5014,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5038,10 +5038,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439310</v>
+        <v>439388</v>
       </c>
       <c r="R44" t="n">
-        <v>6781051</v>
+        <v>6781060</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5103,7 +5103,7 @@
         <v>132013618</v>
       </c>
       <c r="B45" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5201,54 +5201,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132013652</v>
+        <v>132013693</v>
       </c>
       <c r="B46" t="n">
-        <v>8455</v>
+        <v>79319</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439297</v>
+        <v>439233</v>
       </c>
       <c r="R46" t="n">
-        <v>6781233</v>
+        <v>6781356</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5289,7 +5280,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5311,7 +5301,7 @@
         <v>132013622</v>
       </c>
       <c r="B47" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5413,10 +5403,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132013614</v>
+        <v>132013639</v>
       </c>
       <c r="B48" t="n">
-        <v>79936</v>
+        <v>57946</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5424,34 +5414,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439314</v>
+        <v>439388</v>
       </c>
       <c r="R48" t="n">
-        <v>6781147</v>
+        <v>6781058</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5510,10 +5508,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132013693</v>
+        <v>132013614</v>
       </c>
       <c r="B49" t="n">
-        <v>79317</v>
+        <v>79938</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5521,21 +5519,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5545,10 +5543,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439233</v>
+        <v>439314</v>
       </c>
       <c r="R49" t="n">
-        <v>6781356</v>
+        <v>6781147</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5607,40 +5605,41 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132013639</v>
+        <v>132013652</v>
       </c>
       <c r="B50" t="n">
-        <v>57945</v>
+        <v>8455</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -5650,10 +5649,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>439388</v>
+        <v>439297</v>
       </c>
       <c r="R50" t="n">
-        <v>6781058</v>
+        <v>6781233</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5694,6 +5693,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5715,7 +5715,7 @@
         <v>132013677</v>
       </c>
       <c r="B51" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>132013689</v>
       </c>
       <c r="B52" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>132013635</v>
       </c>
       <c r="B53" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6011,41 +6011,40 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132013649</v>
+        <v>132013641</v>
       </c>
       <c r="B54" t="n">
-        <v>8455</v>
+        <v>57946</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6055,10 +6054,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>439252</v>
+        <v>439360</v>
       </c>
       <c r="R54" t="n">
-        <v>6781254</v>
+        <v>6781051</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6099,7 +6098,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6118,10 +6116,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132013641</v>
+        <v>132013644</v>
       </c>
       <c r="B55" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6161,10 +6159,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>439360</v>
+        <v>439349</v>
       </c>
       <c r="R55" t="n">
-        <v>6781051</v>
+        <v>6781004</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6223,10 +6221,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132013644</v>
+        <v>132013615</v>
       </c>
       <c r="B56" t="n">
-        <v>57945</v>
+        <v>79938</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6234,31 +6232,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6266,10 +6259,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>439349</v>
+        <v>439324</v>
       </c>
       <c r="R56" t="n">
-        <v>6781004</v>
+        <v>6781110</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6310,6 +6303,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6328,10 +6322,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132013615</v>
+        <v>132013620</v>
       </c>
       <c r="B57" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6366,10 +6360,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>439324</v>
+        <v>439351</v>
       </c>
       <c r="R57" t="n">
-        <v>6781110</v>
+        <v>6780997</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6429,37 +6423,43 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132013620</v>
+        <v>132013649</v>
       </c>
       <c r="B58" t="n">
-        <v>79936</v>
+        <v>8455</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6467,10 +6467,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439351</v>
+        <v>439252</v>
       </c>
       <c r="R58" t="n">
-        <v>6780997</v>
+        <v>6781254</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 6847-2026 artfynd.xlsx
+++ b/artfynd/A 6847-2026 artfynd.xlsx
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132013627</v>
+        <v>132013612</v>
       </c>
       <c r="B12" t="n">
-        <v>57946</v>
+        <v>79938</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,42 +1716,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439286</v>
+        <v>439240</v>
       </c>
       <c r="R12" t="n">
-        <v>6781084</v>
+        <v>6781353</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,45 +1802,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132013612</v>
+        <v>132013647</v>
       </c>
       <c r="B13" t="n">
-        <v>79938</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439240</v>
+        <v>439266</v>
       </c>
       <c r="R13" t="n">
-        <v>6781353</v>
+        <v>6781130</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,6 +1890,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1907,54 +1909,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132013647</v>
+        <v>132013685</v>
       </c>
       <c r="B14" t="n">
-        <v>8455</v>
+        <v>79319</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439266</v>
+        <v>439329</v>
       </c>
       <c r="R14" t="n">
-        <v>6781130</v>
+        <v>6781100</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,7 +1988,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2014,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132013685</v>
+        <v>132013627</v>
       </c>
       <c r="B15" t="n">
-        <v>79319</v>
+        <v>57946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,34 +2017,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439329</v>
+        <v>439286</v>
       </c>
       <c r="R15" t="n">
-        <v>6781100</v>
+        <v>6781084</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2818,40 +2818,41 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132013640</v>
+        <v>132013661</v>
       </c>
       <c r="B23" t="n">
-        <v>57946</v>
+        <v>8455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2861,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439378</v>
+        <v>439403</v>
       </c>
       <c r="R23" t="n">
-        <v>6781041</v>
+        <v>6781018</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2905,6 +2906,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2923,41 +2925,40 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132013661</v>
+        <v>132013640</v>
       </c>
       <c r="B24" t="n">
-        <v>8455</v>
+        <v>57946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2967,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439403</v>
+        <v>439378</v>
       </c>
       <c r="R24" t="n">
-        <v>6781018</v>
+        <v>6781041</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3011,7 +3012,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -4492,10 +4492,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132013695</v>
+        <v>132013642</v>
       </c>
       <c r="B39" t="n">
-        <v>79319</v>
+        <v>57946</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4503,26 +4503,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4530,10 +4535,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439388</v>
+        <v>439403</v>
       </c>
       <c r="R39" t="n">
-        <v>6781029</v>
+        <v>6781014</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4574,7 +4579,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4593,10 +4597,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132013642</v>
+        <v>132013613</v>
       </c>
       <c r="B40" t="n">
-        <v>57946</v>
+        <v>79938</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4604,31 +4608,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4636,10 +4635,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439403</v>
+        <v>439286</v>
       </c>
       <c r="R40" t="n">
-        <v>6781014</v>
+        <v>6781160</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4680,6 +4679,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4698,37 +4698,43 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132013613</v>
+        <v>132013660</v>
       </c>
       <c r="B41" t="n">
-        <v>79938</v>
+        <v>8455</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4736,10 +4742,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439286</v>
+        <v>439381</v>
       </c>
       <c r="R41" t="n">
-        <v>6781160</v>
+        <v>6781035</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4799,43 +4805,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132013660</v>
+        <v>132013695</v>
       </c>
       <c r="B42" t="n">
-        <v>8455</v>
+        <v>79319</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439381</v>
+        <v>439388</v>
       </c>
       <c r="R42" t="n">
-        <v>6781035</v>
+        <v>6781029</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5201,10 +5201,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132013693</v>
+        <v>132013614</v>
       </c>
       <c r="B46" t="n">
-        <v>79319</v>
+        <v>79938</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5212,21 +5212,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439233</v>
+        <v>439314</v>
       </c>
       <c r="R46" t="n">
-        <v>6781356</v>
+        <v>6781147</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5298,10 +5298,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132013622</v>
+        <v>132013652</v>
       </c>
       <c r="B47" t="n">
-        <v>57137</v>
+        <v>8455</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5309,29 +5309,30 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5341,10 +5342,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439391</v>
+        <v>439297</v>
       </c>
       <c r="R47" t="n">
-        <v>6781007</v>
+        <v>6781233</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5385,6 +5386,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5403,10 +5405,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132013639</v>
+        <v>132013693</v>
       </c>
       <c r="B48" t="n">
-        <v>57946</v>
+        <v>79319</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5414,42 +5416,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439388</v>
+        <v>439233</v>
       </c>
       <c r="R48" t="n">
-        <v>6781058</v>
+        <v>6781356</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5508,10 +5502,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132013614</v>
+        <v>132013639</v>
       </c>
       <c r="B49" t="n">
-        <v>79938</v>
+        <v>57946</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5519,34 +5513,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439314</v>
+        <v>439388</v>
       </c>
       <c r="R49" t="n">
-        <v>6781147</v>
+        <v>6781058</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5605,10 +5607,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132013652</v>
+        <v>132013622</v>
       </c>
       <c r="B50" t="n">
-        <v>8455</v>
+        <v>57137</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5616,30 +5618,29 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -5649,10 +5650,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>439297</v>
+        <v>439391</v>
       </c>
       <c r="R50" t="n">
-        <v>6781233</v>
+        <v>6781007</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5693,7 +5694,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6847-2026 artfynd.xlsx
+++ b/artfynd/A 6847-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132013687</v>
       </c>
       <c r="B2" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132013688</v>
+        <v>132013619</v>
       </c>
       <c r="B6" t="n">
-        <v>79319</v>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439363</v>
+        <v>439376</v>
       </c>
       <c r="R6" t="n">
-        <v>6781030</v>
+        <v>6781031</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132013682</v>
+        <v>132013688</v>
       </c>
       <c r="B7" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439297</v>
+        <v>439363</v>
       </c>
       <c r="R7" t="n">
-        <v>6781183</v>
+        <v>6781030</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132013619</v>
+        <v>132013682</v>
       </c>
       <c r="B8" t="n">
-        <v>79938</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439376</v>
+        <v>439297</v>
       </c>
       <c r="R8" t="n">
-        <v>6781031</v>
+        <v>6781183</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1705,45 +1705,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132013612</v>
+        <v>132013662</v>
       </c>
       <c r="B12" t="n">
-        <v>79938</v>
+        <v>8455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439240</v>
+        <v>439398</v>
       </c>
       <c r="R12" t="n">
-        <v>6781353</v>
+        <v>6781005</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1784,6 +1793,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1909,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132013685</v>
+        <v>132013612</v>
       </c>
       <c r="B14" t="n">
-        <v>79319</v>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439329</v>
+        <v>439240</v>
       </c>
       <c r="R14" t="n">
-        <v>6781100</v>
+        <v>6781353</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132013627</v>
+        <v>132013685</v>
       </c>
       <c r="B15" t="n">
-        <v>57946</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,42 +2027,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439286</v>
+        <v>439329</v>
       </c>
       <c r="R15" t="n">
-        <v>6781084</v>
+        <v>6781100</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2111,41 +2113,40 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132013662</v>
+        <v>132013627</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2155,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439398</v>
+        <v>439286</v>
       </c>
       <c r="R16" t="n">
-        <v>6781005</v>
+        <v>6781084</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,7 +2200,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>132013637</v>
       </c>
       <c r="B17" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>132013676</v>
       </c>
       <c r="B18" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>132013684</v>
       </c>
       <c r="B19" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>132013680</v>
       </c>
       <c r="B21" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>132013675</v>
       </c>
       <c r="B22" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2818,41 +2818,40 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132013661</v>
+        <v>132013640</v>
       </c>
       <c r="B23" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2862,10 +2861,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439403</v>
+        <v>439378</v>
       </c>
       <c r="R23" t="n">
-        <v>6781018</v>
+        <v>6781041</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2906,7 +2905,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2925,40 +2923,41 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132013640</v>
+        <v>132013661</v>
       </c>
       <c r="B24" t="n">
-        <v>57946</v>
+        <v>8455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2968,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439378</v>
+        <v>439403</v>
       </c>
       <c r="R24" t="n">
-        <v>6781041</v>
+        <v>6781018</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3012,6 +3011,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>132013686</v>
       </c>
       <c r="B25" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132013636</v>
+        <v>132013633</v>
       </c>
       <c r="B26" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439308</v>
+        <v>439255</v>
       </c>
       <c r="R26" t="n">
-        <v>6781186</v>
+        <v>6781203</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132013633</v>
+        <v>132013636</v>
       </c>
       <c r="B27" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439255</v>
+        <v>439308</v>
       </c>
       <c r="R27" t="n">
-        <v>6781203</v>
+        <v>6781186</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3453,37 +3453,43 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132013678</v>
+        <v>132013655</v>
       </c>
       <c r="B29" t="n">
-        <v>79319</v>
+        <v>8455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3494,7 +3500,7 @@
         <v>439274</v>
       </c>
       <c r="R29" t="n">
-        <v>6781239</v>
+        <v>6781241</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3554,43 +3560,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132013655</v>
+        <v>132013678</v>
       </c>
       <c r="B30" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>439274</v>
       </c>
       <c r="R30" t="n">
-        <v>6781241</v>
+        <v>6781239</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3661,10 +3661,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132013643</v>
+        <v>132013638</v>
       </c>
       <c r="B31" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439398</v>
+        <v>439341</v>
       </c>
       <c r="R31" t="n">
-        <v>6781005</v>
+        <v>6781087</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3766,10 +3766,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132013638</v>
+        <v>132013643</v>
       </c>
       <c r="B32" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439341</v>
+        <v>439398</v>
       </c>
       <c r="R32" t="n">
-        <v>6781087</v>
+        <v>6781005</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3981,7 +3981,7 @@
         <v>132013628</v>
       </c>
       <c r="B34" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>132013679</v>
       </c>
       <c r="B35" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>132013681</v>
       </c>
       <c r="B36" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>132013631</v>
       </c>
       <c r="B37" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>132013623</v>
       </c>
       <c r="B38" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4492,10 +4492,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132013642</v>
+        <v>132013695</v>
       </c>
       <c r="B39" t="n">
-        <v>57946</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4503,31 +4503,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4535,10 +4530,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439403</v>
+        <v>439388</v>
       </c>
       <c r="R39" t="n">
-        <v>6781014</v>
+        <v>6781029</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4579,6 +4574,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4600,7 +4596,7 @@
         <v>132013613</v>
       </c>
       <c r="B40" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4698,41 +4694,40 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132013660</v>
+        <v>132013642</v>
       </c>
       <c r="B41" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4742,10 +4737,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439381</v>
+        <v>439403</v>
       </c>
       <c r="R41" t="n">
-        <v>6781035</v>
+        <v>6781014</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4786,7 +4781,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4805,37 +4799,43 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132013695</v>
+        <v>132013660</v>
       </c>
       <c r="B42" t="n">
-        <v>79319</v>
+        <v>8455</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439388</v>
+        <v>439381</v>
       </c>
       <c r="R42" t="n">
-        <v>6781029</v>
+        <v>6781035</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4906,10 +4906,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132013674</v>
+        <v>132013617</v>
       </c>
       <c r="B43" t="n">
-        <v>79319</v>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4917,21 +4917,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>439310</v>
+        <v>439388</v>
       </c>
       <c r="R43" t="n">
-        <v>6781051</v>
+        <v>6781060</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5003,10 +5003,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132013617</v>
+        <v>132013674</v>
       </c>
       <c r="B44" t="n">
-        <v>79938</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5014,21 +5014,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5038,10 +5038,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439388</v>
+        <v>439310</v>
       </c>
       <c r="R44" t="n">
-        <v>6781060</v>
+        <v>6781051</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5103,7 +5103,7 @@
         <v>132013618</v>
       </c>
       <c r="B45" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5201,45 +5201,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132013614</v>
+        <v>132013652</v>
       </c>
       <c r="B46" t="n">
-        <v>79938</v>
+        <v>8455</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439314</v>
+        <v>439297</v>
       </c>
       <c r="R46" t="n">
-        <v>6781147</v>
+        <v>6781233</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5280,6 +5289,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5298,41 +5308,40 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132013652</v>
+        <v>132013639</v>
       </c>
       <c r="B47" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5342,10 +5351,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439297</v>
+        <v>439388</v>
       </c>
       <c r="R47" t="n">
-        <v>6781233</v>
+        <v>6781058</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5386,7 +5395,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5405,45 +5413,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132013693</v>
+        <v>132013622</v>
       </c>
       <c r="B48" t="n">
-        <v>79319</v>
+        <v>57141</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439233</v>
+        <v>439391</v>
       </c>
       <c r="R48" t="n">
-        <v>6781356</v>
+        <v>6781007</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5502,10 +5518,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132013639</v>
+        <v>132013614</v>
       </c>
       <c r="B49" t="n">
-        <v>57946</v>
+        <v>79946</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5513,42 +5529,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439388</v>
+        <v>439314</v>
       </c>
       <c r="R49" t="n">
-        <v>6781058</v>
+        <v>6781147</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5607,53 +5615,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132013622</v>
+        <v>132013693</v>
       </c>
       <c r="B50" t="n">
-        <v>57137</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>439391</v>
+        <v>439233</v>
       </c>
       <c r="R50" t="n">
-        <v>6781007</v>
+        <v>6781356</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5715,7 +5715,7 @@
         <v>132013677</v>
       </c>
       <c r="B51" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>132013689</v>
       </c>
       <c r="B52" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>132013635</v>
       </c>
       <c r="B53" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132013641</v>
+        <v>132013615</v>
       </c>
       <c r="B54" t="n">
-        <v>57946</v>
+        <v>79946</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6022,31 +6022,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6054,10 +6049,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>439360</v>
+        <v>439324</v>
       </c>
       <c r="R54" t="n">
-        <v>6781051</v>
+        <v>6781110</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6098,6 +6093,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6116,10 +6112,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132013644</v>
+        <v>132013620</v>
       </c>
       <c r="B55" t="n">
-        <v>57946</v>
+        <v>79946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6127,31 +6123,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6159,10 +6150,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>439349</v>
+        <v>439351</v>
       </c>
       <c r="R55" t="n">
-        <v>6781004</v>
+        <v>6780997</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6203,6 +6194,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6221,10 +6213,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132013615</v>
+        <v>132013641</v>
       </c>
       <c r="B56" t="n">
-        <v>79938</v>
+        <v>57950</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6232,26 +6224,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6259,10 +6256,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>439324</v>
+        <v>439360</v>
       </c>
       <c r="R56" t="n">
-        <v>6781110</v>
+        <v>6781051</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6303,7 +6300,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6322,10 +6318,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132013620</v>
+        <v>132013644</v>
       </c>
       <c r="B57" t="n">
-        <v>79938</v>
+        <v>57950</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6333,26 +6329,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6360,10 +6361,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>439351</v>
+        <v>439349</v>
       </c>
       <c r="R57" t="n">
-        <v>6780997</v>
+        <v>6781004</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6404,7 +6405,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6847-2026 artfynd.xlsx
+++ b/artfynd/A 6847-2026 artfynd.xlsx
@@ -1705,54 +1705,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132013662</v>
+        <v>132013612</v>
       </c>
       <c r="B12" t="n">
-        <v>8455</v>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439398</v>
+        <v>439240</v>
       </c>
       <c r="R12" t="n">
-        <v>6781005</v>
+        <v>6781353</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,7 +1784,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1812,54 +1802,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132013647</v>
+        <v>132013685</v>
       </c>
       <c r="B13" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439266</v>
+        <v>439329</v>
       </c>
       <c r="R13" t="n">
-        <v>6781130</v>
+        <v>6781100</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,7 +1881,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1919,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132013612</v>
+        <v>132013627</v>
       </c>
       <c r="B14" t="n">
-        <v>79946</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1930,34 +1910,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439240</v>
+        <v>439286</v>
       </c>
       <c r="R14" t="n">
-        <v>6781353</v>
+        <v>6781084</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,45 +2004,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132013685</v>
+        <v>132013662</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439329</v>
+        <v>439398</v>
       </c>
       <c r="R15" t="n">
-        <v>6781100</v>
+        <v>6781005</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2095,6 +2092,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2113,40 +2111,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132013627</v>
+        <v>132013647</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>8455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2156,10 +2155,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439286</v>
+        <v>439266</v>
       </c>
       <c r="R16" t="n">
-        <v>6781084</v>
+        <v>6781130</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,6 +2199,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2323,45 +2323,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132013676</v>
+        <v>132013654</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439220</v>
+        <v>439289</v>
       </c>
       <c r="R18" t="n">
-        <v>6781321</v>
+        <v>6781237</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2402,6 +2411,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2420,7 +2430,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132013684</v>
+        <v>132013676</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2455,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439327</v>
+        <v>439220</v>
       </c>
       <c r="R19" t="n">
-        <v>6781115</v>
+        <v>6781321</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2517,54 +2527,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132013654</v>
+        <v>132013684</v>
       </c>
       <c r="B20" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439289</v>
+        <v>439327</v>
       </c>
       <c r="R20" t="n">
-        <v>6781237</v>
+        <v>6781115</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,7 +2606,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3030,37 +3030,43 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132013686</v>
+        <v>132013663</v>
       </c>
       <c r="B25" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3068,10 +3074,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439333</v>
+        <v>439379</v>
       </c>
       <c r="R25" t="n">
-        <v>6781057</v>
+        <v>6781012</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3104,11 +3110,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3136,10 +3137,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132013633</v>
+        <v>132013686</v>
       </c>
       <c r="B26" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,31 +3148,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3179,10 +3175,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439255</v>
+        <v>439333</v>
       </c>
       <c r="R26" t="n">
-        <v>6781203</v>
+        <v>6781057</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3217,12 +3213,18 @@
           <t>2026-03-29</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3241,7 +3243,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132013636</v>
+        <v>132013633</v>
       </c>
       <c r="B27" t="n">
         <v>57950</v>
@@ -3284,10 +3286,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439308</v>
+        <v>439255</v>
       </c>
       <c r="R27" t="n">
-        <v>6781186</v>
+        <v>6781203</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3346,41 +3348,40 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132013663</v>
+        <v>132013636</v>
       </c>
       <c r="B28" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3390,10 +3391,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439379</v>
+        <v>439308</v>
       </c>
       <c r="R28" t="n">
-        <v>6781012</v>
+        <v>6781186</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3434,7 +3435,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6847-2026 artfynd.xlsx
+++ b/artfynd/A 6847-2026 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132013687</v>
+        <v>132013651</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>439367</v>
+        <v>439293</v>
       </c>
       <c r="R2" t="n">
-        <v>6781024</v>
+        <v>6781229</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -986,54 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132013651</v>
+        <v>132013687</v>
       </c>
       <c r="B5" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439293</v>
+        <v>439367</v>
       </c>
       <c r="R5" t="n">
-        <v>6781229</v>
+        <v>6781024</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1075,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1287,45 +1287,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132013682</v>
+        <v>132013648</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439297</v>
+        <v>439237</v>
       </c>
       <c r="R8" t="n">
-        <v>6781183</v>
+        <v>6781292</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,6 +1375,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1384,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132013648</v>
+        <v>132013650</v>
       </c>
       <c r="B9" t="n">
         <v>8455</v>
@@ -1418,7 +1428,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1428,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439237</v>
+        <v>439293</v>
       </c>
       <c r="R9" t="n">
-        <v>6781292</v>
+        <v>6781237</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132013650</v>
+        <v>132013653</v>
       </c>
       <c r="B10" t="n">
         <v>8455</v>
@@ -1525,7 +1535,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1535,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>439293</v>
+        <v>439292</v>
       </c>
       <c r="R10" t="n">
-        <v>6781237</v>
+        <v>6781219</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,54 +1608,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132013653</v>
+        <v>132013682</v>
       </c>
       <c r="B11" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439292</v>
+        <v>439297</v>
       </c>
       <c r="R11" t="n">
-        <v>6781219</v>
+        <v>6781183</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,7 +1687,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1899,40 +1899,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132013627</v>
+        <v>132013662</v>
       </c>
       <c r="B14" t="n">
-        <v>57950</v>
+        <v>8455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1942,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439286</v>
+        <v>439398</v>
       </c>
       <c r="R14" t="n">
-        <v>6781084</v>
+        <v>6781005</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,6 +1987,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2004,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132013662</v>
+        <v>132013647</v>
       </c>
       <c r="B15" t="n">
         <v>8455</v>
@@ -2048,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439398</v>
+        <v>439266</v>
       </c>
       <c r="R15" t="n">
-        <v>6781005</v>
+        <v>6781130</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2111,41 +2113,40 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132013647</v>
+        <v>132013627</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2155,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439266</v>
+        <v>439286</v>
       </c>
       <c r="R16" t="n">
-        <v>6781130</v>
+        <v>6781084</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,7 +2200,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2323,54 +2323,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132013654</v>
+        <v>132013676</v>
       </c>
       <c r="B18" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439289</v>
+        <v>439220</v>
       </c>
       <c r="R18" t="n">
-        <v>6781237</v>
+        <v>6781321</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2411,7 +2402,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2430,7 +2420,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132013676</v>
+        <v>132013684</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2465,10 +2455,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439220</v>
+        <v>439327</v>
       </c>
       <c r="R19" t="n">
-        <v>6781321</v>
+        <v>6781115</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2527,45 +2517,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132013684</v>
+        <v>132013654</v>
       </c>
       <c r="B20" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439327</v>
+        <v>439289</v>
       </c>
       <c r="R20" t="n">
-        <v>6781115</v>
+        <v>6781237</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2606,6 +2605,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2624,45 +2624,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132013680</v>
+        <v>132013661</v>
       </c>
       <c r="B21" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439265</v>
+        <v>439403</v>
       </c>
       <c r="R21" t="n">
-        <v>6781191</v>
+        <v>6781018</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2703,6 +2712,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2721,7 +2731,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132013675</v>
+        <v>132013680</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -2756,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439249</v>
+        <v>439265</v>
       </c>
       <c r="R22" t="n">
-        <v>6781169</v>
+        <v>6781191</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132013640</v>
+        <v>132013675</v>
       </c>
       <c r="B23" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2829,42 +2839,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439378</v>
+        <v>439249</v>
       </c>
       <c r="R23" t="n">
-        <v>6781041</v>
+        <v>6781169</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,41 +2925,40 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132013661</v>
+        <v>132013640</v>
       </c>
       <c r="B24" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2967,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439403</v>
+        <v>439378</v>
       </c>
       <c r="R24" t="n">
-        <v>6781018</v>
+        <v>6781041</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3011,7 +3012,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3030,43 +3030,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132013663</v>
+        <v>132013686</v>
       </c>
       <c r="B25" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3074,10 +3068,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439379</v>
+        <v>439333</v>
       </c>
       <c r="R25" t="n">
-        <v>6781012</v>
+        <v>6781057</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3110,6 +3104,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3137,10 +3136,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132013686</v>
+        <v>132013633</v>
       </c>
       <c r="B26" t="n">
-        <v>79327</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3148,26 +3147,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3175,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439333</v>
+        <v>439255</v>
       </c>
       <c r="R26" t="n">
-        <v>6781057</v>
+        <v>6781203</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3213,18 +3217,12 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3243,7 +3241,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132013633</v>
+        <v>132013636</v>
       </c>
       <c r="B27" t="n">
         <v>57950</v>
@@ -3286,10 +3284,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439255</v>
+        <v>439308</v>
       </c>
       <c r="R27" t="n">
-        <v>6781203</v>
+        <v>6781186</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3348,40 +3346,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132013636</v>
+        <v>132013663</v>
       </c>
       <c r="B28" t="n">
-        <v>57950</v>
+        <v>8455</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3391,10 +3390,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439308</v>
+        <v>439379</v>
       </c>
       <c r="R28" t="n">
-        <v>6781186</v>
+        <v>6781012</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3435,6 +3434,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3453,43 +3453,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132013655</v>
+        <v>132013678</v>
       </c>
       <c r="B29" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3500,7 +3494,7 @@
         <v>439274</v>
       </c>
       <c r="R29" t="n">
-        <v>6781241</v>
+        <v>6781239</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3560,37 +3554,43 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132013678</v>
+        <v>132013655</v>
       </c>
       <c r="B30" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>439274</v>
       </c>
       <c r="R30" t="n">
-        <v>6781239</v>
+        <v>6781241</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4492,10 +4492,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132013695</v>
+        <v>132013642</v>
       </c>
       <c r="B39" t="n">
-        <v>79327</v>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4503,26 +4503,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4530,10 +4535,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439388</v>
+        <v>439403</v>
       </c>
       <c r="R39" t="n">
-        <v>6781029</v>
+        <v>6781014</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4574,7 +4579,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4593,37 +4597,43 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132013613</v>
+        <v>132013660</v>
       </c>
       <c r="B40" t="n">
-        <v>79946</v>
+        <v>8455</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4631,10 +4641,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439286</v>
+        <v>439381</v>
       </c>
       <c r="R40" t="n">
-        <v>6781160</v>
+        <v>6781035</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4694,10 +4704,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132013642</v>
+        <v>132013695</v>
       </c>
       <c r="B41" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4705,31 +4715,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4737,10 +4742,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439403</v>
+        <v>439388</v>
       </c>
       <c r="R41" t="n">
-        <v>6781014</v>
+        <v>6781029</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4781,6 +4786,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4799,43 +4805,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132013660</v>
+        <v>132013613</v>
       </c>
       <c r="B42" t="n">
-        <v>8455</v>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439381</v>
+        <v>439286</v>
       </c>
       <c r="R42" t="n">
-        <v>6781035</v>
+        <v>6781160</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5201,54 +5201,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132013652</v>
+        <v>132013614</v>
       </c>
       <c r="B46" t="n">
-        <v>8455</v>
+        <v>79946</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439297</v>
+        <v>439314</v>
       </c>
       <c r="R46" t="n">
-        <v>6781233</v>
+        <v>6781147</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5289,7 +5280,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5308,10 +5298,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132013639</v>
+        <v>132013693</v>
       </c>
       <c r="B47" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5319,42 +5309,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439388</v>
+        <v>439233</v>
       </c>
       <c r="R47" t="n">
-        <v>6781058</v>
+        <v>6781356</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5518,10 +5500,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132013614</v>
+        <v>132013639</v>
       </c>
       <c r="B49" t="n">
-        <v>79946</v>
+        <v>57950</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5529,34 +5511,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439314</v>
+        <v>439388</v>
       </c>
       <c r="R49" t="n">
-        <v>6781147</v>
+        <v>6781058</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5615,45 +5605,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132013693</v>
+        <v>132013652</v>
       </c>
       <c r="B50" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>439233</v>
+        <v>439297</v>
       </c>
       <c r="R50" t="n">
-        <v>6781356</v>
+        <v>6781233</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5694,6 +5693,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6011,10 +6011,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132013615</v>
+        <v>132013641</v>
       </c>
       <c r="B54" t="n">
-        <v>79946</v>
+        <v>57950</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6022,26 +6022,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6049,10 +6054,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>439324</v>
+        <v>439360</v>
       </c>
       <c r="R54" t="n">
-        <v>6781110</v>
+        <v>6781051</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6093,7 +6098,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6112,10 +6116,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132013620</v>
+        <v>132013644</v>
       </c>
       <c r="B55" t="n">
-        <v>79946</v>
+        <v>57950</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6123,26 +6127,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6150,10 +6159,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>439351</v>
+        <v>439349</v>
       </c>
       <c r="R55" t="n">
-        <v>6780997</v>
+        <v>6781004</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6194,7 +6203,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6213,40 +6221,41 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132013641</v>
+        <v>132013649</v>
       </c>
       <c r="B56" t="n">
-        <v>57950</v>
+        <v>8455</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6256,10 +6265,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>439360</v>
+        <v>439252</v>
       </c>
       <c r="R56" t="n">
-        <v>6781051</v>
+        <v>6781254</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6300,6 +6309,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6318,10 +6328,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132013644</v>
+        <v>132013615</v>
       </c>
       <c r="B57" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6329,31 +6339,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6361,10 +6366,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>439349</v>
+        <v>439324</v>
       </c>
       <c r="R57" t="n">
-        <v>6781004</v>
+        <v>6781110</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6405,6 +6410,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6423,43 +6429,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132013649</v>
+        <v>132013620</v>
       </c>
       <c r="B58" t="n">
-        <v>8455</v>
+        <v>79946</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6467,10 +6467,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439252</v>
+        <v>439351</v>
       </c>
       <c r="R58" t="n">
-        <v>6781254</v>
+        <v>6780997</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 6847-2026 artfynd.xlsx
+++ b/artfynd/A 6847-2026 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132013651</v>
+        <v>132013687</v>
       </c>
       <c r="B2" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>439293</v>
+        <v>439367</v>
       </c>
       <c r="R2" t="n">
-        <v>6781229</v>
+        <v>6781024</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132013659</v>
+        <v>132013651</v>
       </c>
       <c r="B3" t="n">
         <v>8455</v>
@@ -816,7 +806,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439359</v>
+        <v>439293</v>
       </c>
       <c r="R3" t="n">
-        <v>6781091</v>
+        <v>6781229</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132013656</v>
+        <v>132013659</v>
       </c>
       <c r="B4" t="n">
         <v>8455</v>
@@ -923,7 +913,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -933,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439249</v>
+        <v>439359</v>
       </c>
       <c r="R4" t="n">
-        <v>6781191</v>
+        <v>6781091</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,45 +986,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132013687</v>
+        <v>132013656</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439367</v>
+        <v>439249</v>
       </c>
       <c r="R5" t="n">
-        <v>6781024</v>
+        <v>6781191</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,6 +1074,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1287,54 +1287,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132013648</v>
+        <v>132013682</v>
       </c>
       <c r="B8" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439237</v>
+        <v>439297</v>
       </c>
       <c r="R8" t="n">
-        <v>6781292</v>
+        <v>6781183</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,7 +1366,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1394,7 +1384,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132013650</v>
+        <v>132013648</v>
       </c>
       <c r="B9" t="n">
         <v>8455</v>
@@ -1428,7 +1418,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1438,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439293</v>
+        <v>439237</v>
       </c>
       <c r="R9" t="n">
-        <v>6781237</v>
+        <v>6781292</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132013653</v>
+        <v>132013650</v>
       </c>
       <c r="B10" t="n">
         <v>8455</v>
@@ -1535,7 +1525,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1545,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>439292</v>
+        <v>439293</v>
       </c>
       <c r="R10" t="n">
-        <v>6781219</v>
+        <v>6781237</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,45 +1598,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132013682</v>
+        <v>132013653</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439297</v>
+        <v>439292</v>
       </c>
       <c r="R11" t="n">
-        <v>6781183</v>
+        <v>6781219</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1687,6 +1686,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1899,41 +1899,40 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132013662</v>
+        <v>132013627</v>
       </c>
       <c r="B14" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1943,10 +1942,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439398</v>
+        <v>439286</v>
       </c>
       <c r="R14" t="n">
-        <v>6781005</v>
+        <v>6781084</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1987,7 +1986,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2113,40 +2111,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132013627</v>
+        <v>132013662</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>8455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2156,10 +2155,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439286</v>
+        <v>439398</v>
       </c>
       <c r="R16" t="n">
-        <v>6781084</v>
+        <v>6781005</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,6 +2199,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -5201,10 +5201,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132013614</v>
+        <v>132013639</v>
       </c>
       <c r="B46" t="n">
-        <v>79946</v>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5212,34 +5212,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439314</v>
+        <v>439388</v>
       </c>
       <c r="R46" t="n">
-        <v>6781147</v>
+        <v>6781058</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5298,45 +5306,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132013693</v>
+        <v>132013622</v>
       </c>
       <c r="B47" t="n">
-        <v>79327</v>
+        <v>57141</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439233</v>
+        <v>439391</v>
       </c>
       <c r="R47" t="n">
-        <v>6781356</v>
+        <v>6781007</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5395,53 +5411,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132013622</v>
+        <v>132013614</v>
       </c>
       <c r="B48" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439391</v>
+        <v>439314</v>
       </c>
       <c r="R48" t="n">
-        <v>6781007</v>
+        <v>6781147</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5500,10 +5508,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132013639</v>
+        <v>132013693</v>
       </c>
       <c r="B49" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5511,42 +5519,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439388</v>
+        <v>439233</v>
       </c>
       <c r="R49" t="n">
-        <v>6781058</v>
+        <v>6781356</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 6847-2026 artfynd.xlsx
+++ b/artfynd/A 6847-2026 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132013687</v>
+        <v>132013659</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>439367</v>
+        <v>439359</v>
       </c>
       <c r="R2" t="n">
-        <v>6781024</v>
+        <v>6781091</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132013651</v>
+        <v>132013656</v>
       </c>
       <c r="B3" t="n">
         <v>8455</v>
@@ -816,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439293</v>
+        <v>439249</v>
       </c>
       <c r="R3" t="n">
-        <v>6781229</v>
+        <v>6781191</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132013659</v>
+        <v>132013651</v>
       </c>
       <c r="B4" t="n">
         <v>8455</v>
@@ -913,7 +923,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -923,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439359</v>
+        <v>439293</v>
       </c>
       <c r="R4" t="n">
-        <v>6781091</v>
+        <v>6781229</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,54 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132013656</v>
+        <v>132013687</v>
       </c>
       <c r="B5" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439249</v>
+        <v>439367</v>
       </c>
       <c r="R5" t="n">
-        <v>6781191</v>
+        <v>6781024</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1075,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1093,45 +1093,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132013619</v>
+        <v>132013648</v>
       </c>
       <c r="B6" t="n">
-        <v>79946</v>
+        <v>8455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439376</v>
+        <v>439237</v>
       </c>
       <c r="R6" t="n">
-        <v>6781031</v>
+        <v>6781292</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,6 +1181,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1190,45 +1200,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132013688</v>
+        <v>132013650</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439363</v>
+        <v>439293</v>
       </c>
       <c r="R7" t="n">
-        <v>6781030</v>
+        <v>6781237</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,6 +1288,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1287,45 +1307,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132013682</v>
+        <v>132013653</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439297</v>
+        <v>439292</v>
       </c>
       <c r="R8" t="n">
-        <v>6781183</v>
+        <v>6781219</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,6 +1395,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1384,54 +1414,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132013648</v>
+        <v>132013688</v>
       </c>
       <c r="B9" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439237</v>
+        <v>439363</v>
       </c>
       <c r="R9" t="n">
-        <v>6781292</v>
+        <v>6781030</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,7 +1493,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1491,54 +1511,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132013650</v>
+        <v>132013682</v>
       </c>
       <c r="B10" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>439293</v>
+        <v>439297</v>
       </c>
       <c r="R10" t="n">
-        <v>6781237</v>
+        <v>6781183</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,7 +1590,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1598,54 +1608,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132013653</v>
+        <v>132013619</v>
       </c>
       <c r="B11" t="n">
-        <v>8455</v>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439292</v>
+        <v>439376</v>
       </c>
       <c r="R11" t="n">
-        <v>6781219</v>
+        <v>6781031</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,7 +1687,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132013612</v>
+        <v>132013685</v>
       </c>
       <c r="B12" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439240</v>
+        <v>439329</v>
       </c>
       <c r="R12" t="n">
-        <v>6781353</v>
+        <v>6781100</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132013685</v>
+        <v>132013612</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439329</v>
+        <v>439240</v>
       </c>
       <c r="R13" t="n">
-        <v>6781100</v>
+        <v>6781353</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2004,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132013647</v>
+        <v>132013662</v>
       </c>
       <c r="B15" t="n">
         <v>8455</v>
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439266</v>
+        <v>439398</v>
       </c>
       <c r="R15" t="n">
-        <v>6781130</v>
+        <v>6781005</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132013662</v>
+        <v>132013647</v>
       </c>
       <c r="B16" t="n">
         <v>8455</v>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439398</v>
+        <v>439266</v>
       </c>
       <c r="R16" t="n">
-        <v>6781005</v>
+        <v>6781130</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3661,7 +3661,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132013638</v>
+        <v>132013643</v>
       </c>
       <c r="B31" t="n">
         <v>57950</v>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439341</v>
+        <v>439398</v>
       </c>
       <c r="R31" t="n">
-        <v>6781087</v>
+        <v>6781005</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3766,7 +3766,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132013643</v>
+        <v>132013638</v>
       </c>
       <c r="B32" t="n">
         <v>57950</v>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439398</v>
+        <v>439341</v>
       </c>
       <c r="R32" t="n">
-        <v>6781005</v>
+        <v>6781087</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4492,10 +4492,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132013642</v>
+        <v>132013695</v>
       </c>
       <c r="B39" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4503,31 +4503,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4535,10 +4530,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439403</v>
+        <v>439388</v>
       </c>
       <c r="R39" t="n">
-        <v>6781014</v>
+        <v>6781029</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4579,6 +4574,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4597,43 +4593,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132013660</v>
+        <v>132013613</v>
       </c>
       <c r="B40" t="n">
-        <v>8455</v>
+        <v>79946</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4641,10 +4631,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439381</v>
+        <v>439286</v>
       </c>
       <c r="R40" t="n">
-        <v>6781035</v>
+        <v>6781160</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4704,10 +4694,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132013695</v>
+        <v>132013642</v>
       </c>
       <c r="B41" t="n">
-        <v>79327</v>
+        <v>57950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4715,26 +4705,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4742,10 +4737,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439388</v>
+        <v>439403</v>
       </c>
       <c r="R41" t="n">
-        <v>6781029</v>
+        <v>6781014</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4786,7 +4781,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4805,37 +4799,43 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132013613</v>
+        <v>132013660</v>
       </c>
       <c r="B42" t="n">
-        <v>79946</v>
+        <v>8455</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439286</v>
+        <v>439381</v>
       </c>
       <c r="R42" t="n">
-        <v>6781160</v>
+        <v>6781035</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5201,10 +5201,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132013639</v>
+        <v>132013693</v>
       </c>
       <c r="B46" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5212,42 +5212,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439388</v>
+        <v>439233</v>
       </c>
       <c r="R46" t="n">
-        <v>6781058</v>
+        <v>6781356</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5306,53 +5298,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132013622</v>
+        <v>132013614</v>
       </c>
       <c r="B47" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439391</v>
+        <v>439314</v>
       </c>
       <c r="R47" t="n">
-        <v>6781007</v>
+        <v>6781147</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5411,45 +5395,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132013614</v>
+        <v>132013622</v>
       </c>
       <c r="B48" t="n">
-        <v>79946</v>
+        <v>57141</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439314</v>
+        <v>439391</v>
       </c>
       <c r="R48" t="n">
-        <v>6781147</v>
+        <v>6781007</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5508,45 +5500,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132013693</v>
+        <v>132013652</v>
       </c>
       <c r="B49" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lill-Käringberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439233</v>
+        <v>439297</v>
       </c>
       <c r="R49" t="n">
-        <v>6781356</v>
+        <v>6781233</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5587,6 +5588,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5605,41 +5607,40 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132013652</v>
+        <v>132013639</v>
       </c>
       <c r="B50" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -5649,10 +5650,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>439297</v>
+        <v>439388</v>
       </c>
       <c r="R50" t="n">
-        <v>6781233</v>
+        <v>6781058</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5693,7 +5694,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6011,40 +6011,41 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132013641</v>
+        <v>132013649</v>
       </c>
       <c r="B54" t="n">
-        <v>57950</v>
+        <v>8455</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6054,10 +6055,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>439360</v>
+        <v>439252</v>
       </c>
       <c r="R54" t="n">
-        <v>6781051</v>
+        <v>6781254</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6098,6 +6099,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6116,10 +6118,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132013644</v>
+        <v>132013615</v>
       </c>
       <c r="B55" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6127,31 +6129,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6159,10 +6156,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>439349</v>
+        <v>439324</v>
       </c>
       <c r="R55" t="n">
-        <v>6781004</v>
+        <v>6781110</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6203,6 +6200,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6221,43 +6219,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132013649</v>
+        <v>132013620</v>
       </c>
       <c r="B56" t="n">
-        <v>8455</v>
+        <v>79946</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6265,10 +6257,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>439252</v>
+        <v>439351</v>
       </c>
       <c r="R56" t="n">
-        <v>6781254</v>
+        <v>6780997</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6328,10 +6320,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132013615</v>
+        <v>132013644</v>
       </c>
       <c r="B57" t="n">
-        <v>79946</v>
+        <v>57950</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6339,26 +6331,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6366,10 +6363,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>439324</v>
+        <v>439349</v>
       </c>
       <c r="R57" t="n">
-        <v>6781110</v>
+        <v>6781004</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6410,7 +6407,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6429,10 +6425,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132013620</v>
+        <v>132013641</v>
       </c>
       <c r="B58" t="n">
-        <v>79946</v>
+        <v>57950</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6440,26 +6436,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6467,10 +6468,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>439351</v>
+        <v>439360</v>
       </c>
       <c r="R58" t="n">
-        <v>6780997</v>
+        <v>6781051</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6511,7 +6512,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6847-2026 artfynd.xlsx
+++ b/artfynd/A 6847-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AZ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013624</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013674</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013675</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013676</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013677</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,6 +1297,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013678</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1364,6 +1399,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013679</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1461,6 +1501,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013680</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013681</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1660,6 +1710,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013682</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1757,6 +1812,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013684</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1854,6 +1914,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013685</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1960,6 +2025,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013686</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2057,6 +2127,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013687</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2154,6 +2229,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013688</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2251,6 +2331,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013689</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2348,6 +2433,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013690</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2445,6 +2535,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013692</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2542,6 +2637,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013693</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2643,6 +2743,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013695</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2740,6 +2845,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013612</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2841,6 +2951,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013613</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2938,6 +3053,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013614</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3039,6 +3159,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013615</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3136,6 +3261,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013617</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3237,6 +3367,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013618</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3334,6 +3469,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013619</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3435,6 +3575,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013620</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3540,6 +3685,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013627</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3645,6 +3795,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013628</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3750,6 +3905,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013630</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3855,6 +4015,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013631</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3960,6 +4125,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013633</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4065,6 +4235,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013635</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4170,6 +4345,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013636</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4275,6 +4455,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013637</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4380,6 +4565,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013638</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4485,6 +4675,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013639</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4590,6 +4785,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013640</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4695,6 +4895,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013641</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4800,6 +5005,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013642</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4905,6 +5115,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013643</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5010,6 +5225,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013644</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5115,6 +5335,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013645</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5220,6 +5445,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013622</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5325,6 +5555,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013623</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5432,6 +5667,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013647</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5539,6 +5779,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013648</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5646,6 +5891,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013649</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5753,6 +6003,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013650</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5860,6 +6115,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013651</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5967,6 +6227,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013652</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6074,6 +6339,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013653</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6181,6 +6451,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013654</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6288,6 +6563,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013655</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6395,6 +6675,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013656</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6502,6 +6787,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013657</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6609,6 +6899,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013659</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6716,6 +7011,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013660</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6823,6 +7123,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013661</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6930,6 +7235,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013662</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7037,6 +7347,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013663</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7144,6 +7459,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013664</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7249,8 +7569,79 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132013610</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>